--- a/registers/Virginia_Grid_Analysis_Tracker_updated.xlsx
+++ b/registers/Virginia_Grid_Analysis_Tracker_updated.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2472,6 +2472,90 @@
       <c r="F86" t="inlineStr">
         <is>
           <t>NS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>22</v>
+      </c>
+      <c r="B87" t="n">
+        <v>81</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Adequacy metrics: LOLH and unserved energy reported</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>reliability_metrics.py per NERC Risk Mitigation for Emerging Large Loads (2026). Duration and magnitude from the hourly unserved series every solve already produces. Named as realisations, not expectations.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>23</v>
+      </c>
+      <c r="B88" t="n">
+        <v>82</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Forced-outage draws for probabilistic adequacy (LOLE, CVaR)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CVaR at 95% needs 20+ scenarios for one tail observation and several hundred for stability; eight weather years give 0.4. The gap closes with forced-outage draws on the eight already held -- 8 x 100 = 800 scenarios, in NERC range. Needs per-unit forced outage rates from EIA-860 / NERC GADS and a draw loop around the existing solve.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>24</v>
+      </c>
+      <c r="B89" t="n">
+        <v>83</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Reconcile Scenario 2 published run with the bounded run</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>The published path leaves gas at the 200,000 MW default so reports zero unserved; the bounded run shows 30.05 TWh. Measured: 9,000 MW of CCGT closes the gap entirely and takes the existing CT fleet from 100% capacity factor to 0%. Needs the capacity pinned, the CCGT costed, and the two runs made one.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>IP</t>
         </is>
       </c>
     </row>

--- a/registers/Virginia_Grid_Analysis_Tracker_updated.xlsx
+++ b/registers/Virginia_Grid_Analysis_Tracker_updated.xlsx
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>The published path leaves gas at the 200,000 MW default so reports zero unserved; the bounded run shows 30.05 TWh. Measured: 9,000 MW of CCGT closes the gap entirely and takes the existing CT fleet from 100% capacity factor to 0%. Needs the capacity pinned, the CCGT costed, and the two runs made one.</t>
+          <t>Dashboard step 6. The published path leaves gas at the 200,000 MW default so reports zero unserved; the bounded run shows 30.05 TWh. Measured: 6,500 MW of CCGT is the cost optimum (5,000 MW is the adequacy floor), built as six H-Class 1,083 MW units for 6,498 MW. Needs the capacity pinned per year, the units costed, and the two runs made one. Blocks dashboard steps 7-10 and 12.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
